--- a/raw/1972election.xlsx
+++ b/raw/1972election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2467F53B-5099-D041-AAD4-4C85409C7CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52CE81F-0EE5-1941-9FED-671D3AD21CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1620" windowWidth="16380" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28632,7 +28632,7 @@
         <v>8</v>
       </c>
       <c r="G971">
-        <v>138965</v>
+        <v>83134</v>
       </c>
     </row>
     <row r="972" spans="1:7">
@@ -28655,7 +28655,7 @@
         <v>10</v>
       </c>
       <c r="G972">
-        <v>83134</v>
+        <v>138965</v>
       </c>
     </row>
     <row r="973" spans="1:7">
